--- a/GameData/tables/17_Character.xlsx
+++ b/GameData/tables/17_Character.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_behaviour" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'unit_art'!$A$1:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'unit_behaviour'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'unit_art'!$A$1:$I$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'unit_behaviour'!$A$1:$F$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -526,17 +526,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="15.2" customWidth="1" min="2" max="2"/>
-    <col width="15.2" customWidth="1" min="3" max="3"/>
-    <col width="15.2" customWidth="1" min="4" max="4"/>
-    <col width="15.2" customWidth="1" min="5" max="5"/>
-    <col width="16.4" customWidth="1" min="6" max="6"/>
-    <col width="16.4" customWidth="1" min="7" max="7"/>
-    <col width="16.4" customWidth="1" min="8" max="8"/>
+    <col width="11.6" customWidth="1" min="1" max="1"/>
+    <col width="17.6" customWidth="1" min="2" max="2"/>
+    <col width="17.6" customWidth="1" min="3" max="3"/>
+    <col width="17.6" customWidth="1" min="4" max="4"/>
+    <col width="17.6" customWidth="1" min="5" max="5"/>
+    <col width="18.8" customWidth="1" min="6" max="6"/>
+    <col width="18.8" customWidth="1" min="7" max="7"/>
+    <col width="18.8" customWidth="1" min="8" max="8"/>
     <col width="12.8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -590,49 +590,17 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t># 가전 ID(unit.id 과 일치)</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>전투/로비 치비 파일명(Art/Sprites/&lt;이름&gt;.png)</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>전신 일러스트</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>삼면도</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>설정화</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>표정 1</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>표정 2</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>표정 3</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>로비 방에서 걷는 속도(화면 비율/초)</t>
-        </is>
-      </c>
+          <t xml:space="preserve"># </t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr"/>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -1174,8 +1142,188 @@
         <v>0.18</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>blender</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>unit_blender</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>blender_full</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>blender_turn</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>blender_keys</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>blender_face1</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>blender_face2</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>blender_face3</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>unit_purifier</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>purifier_full</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>purifier_turn</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>purifier_keys</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>purifier_face1</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>purifier_face2</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>purifier_face3</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>unit_router</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>router_full</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>router_turn</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>router_keys</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>router_face1</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>router_face2</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>router_face3</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>tv</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>unit_tv</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>tv_full</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>tv_turn</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>tv_keys</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>tv_face1</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>tv_face2</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>tv_face3</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I14"/>
+  <autoFilter ref="A1:I18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1186,10 +1334,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11.6" customWidth="1" min="1" max="1"/>
     <col width="10.4" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="11.6" customWidth="1" min="4" max="4"/>
@@ -1232,34 +1380,14 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t># 가전 ID</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>디펜스 전용 동작 키(비우면 평범한 사거리 공격)</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>대청소 리더 동작 키(비우면 리더 불가)</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>대청소 동료 동작 키(비우면 공격 안 함)</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>1 이면 지원형(대청소에서 적을 때리지 않음)</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>이 동작이 요구하는 skill_param 키 목록(쉼표 구분)</t>
-        </is>
-      </c>
+          <t xml:space="preserve"># </t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr"/>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -1541,8 +1669,64 @@
       </c>
       <c r="F14" s="6" t="n"/>
     </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>blender</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>tv</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F14"/>
+  <autoFilter ref="A1:F18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/GameData/tables/17_Character.xlsx
+++ b/GameData/tables/17_Character.xlsx
@@ -1338,7 +1338,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.6" customWidth="1" min="1" max="1"/>
-    <col width="10.4" customWidth="1" min="2" max="2"/>
+    <col width="11.6" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="11.6" customWidth="1" min="4" max="4"/>
     <col width="10.4" customWidth="1" min="5" max="5"/>
@@ -1675,13 +1675,21 @@
           <t>blender</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>blender</t>
+        </is>
+      </c>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="6" t="n"/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>execHp,execBonus,grindItvMul,grindRadius</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1689,13 +1697,21 @@
           <t>purifier</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="6" t="n"/>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>airMul,tick,skillDmg,skillSlow,skillSlowSec</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1703,13 +1719,21 @@
           <t>router</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="6" t="n"/>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>chainN,chainRange,chainDecay,skillChainAdd,skillItvMul,stun</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1717,13 +1741,21 @@
           <t>tv</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>tv</t>
+        </is>
+      </c>
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="6" t="n"/>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>adMin,adVuln,vulnSec,splashRadius</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F18"/>

--- a/GameData/tables/17_Character.xlsx
+++ b/GameData/tables/17_Character.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_behaviour" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'unit_art'!$A$1:$I$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'unit_art'!$A$1:$J$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'unit_behaviour'!$A$1:$F$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.6" customWidth="1" min="1" max="1"/>
@@ -538,6 +538,7 @@
     <col width="18.8" customWidth="1" min="7" max="7"/>
     <col width="18.8" customWidth="1" min="8" max="8"/>
     <col width="12.8" customWidth="1" min="9" max="9"/>
+    <col width="15.2" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -584,6 +585,11 @@
       <c r="I1" s="3" t="inlineStr">
         <is>
           <t>roomSpeed</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>motionScale</t>
         </is>
       </c>
     </row>
@@ -601,6 +607,7 @@
       <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr"/>
       <c r="I2" s="4" t="inlineStr"/>
+      <c r="J2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -646,6 +653,9 @@
       <c r="I3" s="6" t="n">
         <v>0.18</v>
       </c>
+      <c r="J3" s="6" t="n">
+        <v>1.0318</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -691,6 +701,9 @@
       <c r="I4" s="6" t="n">
         <v>0.26</v>
       </c>
+      <c r="J4" s="6" t="n">
+        <v>1.071649</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -736,6 +749,9 @@
       <c r="I5" s="6" t="n">
         <v>0.12</v>
       </c>
+      <c r="J5" s="6" t="n">
+        <v>1.144792</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -781,6 +797,9 @@
       <c r="I6" s="6" t="n">
         <v>0.18</v>
       </c>
+      <c r="J6" s="6" t="n">
+        <v>1.050237</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -826,6 +845,9 @@
       <c r="I7" s="6" t="n">
         <v>0.18</v>
       </c>
+      <c r="J7" s="6" t="n">
+        <v>1.090907</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -871,6 +893,9 @@
       <c r="I8" s="6" t="n">
         <v>0.12</v>
       </c>
+      <c r="J8" s="6" t="n">
+        <v>1.110089</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -916,6 +941,9 @@
       <c r="I9" s="6" t="n">
         <v>0.18</v>
       </c>
+      <c r="J9" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -961,6 +989,9 @@
       <c r="I10" s="6" t="n">
         <v>0.18</v>
       </c>
+      <c r="J10" s="6" t="n">
+        <v>1.130366</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1006,6 +1037,9 @@
       <c r="I11" s="6" t="n">
         <v>0.18</v>
       </c>
+      <c r="J11" s="6" t="n">
+        <v>1.017925</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1051,6 +1085,9 @@
       <c r="I12" s="6" t="n">
         <v>0.18</v>
       </c>
+      <c r="J12" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1096,6 +1133,9 @@
       <c r="I13" s="6" t="n">
         <v>0.18</v>
       </c>
+      <c r="J13" s="6" t="n">
+        <v>1.092182</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1141,6 +1181,9 @@
       <c r="I14" s="6" t="n">
         <v>0.18</v>
       </c>
+      <c r="J14" s="6" t="n">
+        <v>1.195356</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1186,6 +1229,9 @@
       <c r="I15" s="6" t="n">
         <v>0.18</v>
       </c>
+      <c r="J15" s="6" t="n">
+        <v>1.028333</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1231,6 +1277,9 @@
       <c r="I16" s="6" t="n">
         <v>0.18</v>
       </c>
+      <c r="J16" s="6" t="n">
+        <v>1.037666</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1276,6 +1325,9 @@
       <c r="I17" s="6" t="n">
         <v>0.18</v>
       </c>
+      <c r="J17" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1321,9 +1373,12 @@
       <c r="I18" s="6" t="n">
         <v>0.18</v>
       </c>
+      <c r="J18" s="6" t="n">
+        <v>1.022665</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I18"/>
+  <autoFilter ref="A1:J18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
